--- a/Kitap1.xlsx
+++ b/Kitap1.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D70FF3D6-D706-4460-B1D2-FCEB6A0E574C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DCB98D-D58E-48D4-86B9-4365660152BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="660" windowWidth="24240" windowHeight="12360" xr2:uid="{671C7B34-E544-4FEC-844A-9FD77A9C4109}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" firstSheet="1" activeTab="1" xr2:uid="{671C7B34-E544-4FEC-844A-9FD77A9C4109}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa1" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Sayfa2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="46">
   <si>
     <t>Ad</t>
   </si>
@@ -96,15 +97,6 @@
     <t>AYDIN</t>
   </si>
   <si>
-    <t>NEDA</t>
-  </si>
-  <si>
-    <t>BAYERLI</t>
-  </si>
-  <si>
-    <t>haftaya gelecek</t>
-  </si>
-  <si>
     <t>DİLEK</t>
   </si>
   <si>
@@ -145,6 +137,42 @@
   </si>
   <si>
     <t>iptal</t>
+  </si>
+  <si>
+    <t>SONGÜL</t>
+  </si>
+  <si>
+    <t>TOPCU</t>
+  </si>
+  <si>
+    <t>GÜNEŞ</t>
+  </si>
+  <si>
+    <t>CANAN</t>
+  </si>
+  <si>
+    <t>MAIWAND</t>
+  </si>
+  <si>
+    <t>HOTAK</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>Salı gelecek</t>
+  </si>
+  <si>
+    <t>gelmesini bekliyorum</t>
+  </si>
+  <si>
+    <t>1-2 gün içinde gelecek</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -186,7 +214,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -194,15 +222,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,10 +565,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59563722-F88D-47F5-B54F-1B8C075841A1}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -528,7 +587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -539,10 +598,23 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="6">
+        <v>46125</v>
+      </c>
+      <c r="N2" s="6">
+        <v>46126</v>
+      </c>
+      <c r="O2" s="6">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -555,8 +627,27 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="4">
+        <v>5058994210</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -569,8 +660,27 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I4" s="4">
+        <v>2</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="4">
+        <v>5051184191</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -583,8 +693,27 @@
       <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I5" s="4">
+        <v>3</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="4">
+        <v>5364063837</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -597,8 +726,27 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I6" s="4">
+        <v>4</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="4">
+        <v>5424457265</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -611,8 +759,27 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I7" s="4">
+        <v>5</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="4">
+        <v>5365864841</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -625,22 +792,60 @@
       <c r="D8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I8" s="4">
+        <v>6</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="4">
+        <v>5355893168</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I9" s="4">
+        <v>7</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="4">
+        <v>5070496100</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -653,64 +858,97 @@
       <c r="D10" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="I10" s="4">
+        <v>8</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="4">
+        <v>5336208652</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="4">
+        <v>9</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="4">
+        <v>5389158137</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" t="s">
         <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFB170F-5734-4D5D-94BB-4CFD487EC6E2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>